--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487762_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487762_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.230499999999999</v>
+        <v>7.5479</v>
       </c>
       <c r="E2" t="n">
-        <v>8.3797</v>
+        <v>7.8439</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.1492</v>
+        <v>-0.296</v>
       </c>
       <c r="G2" t="n">
         <v>7.7054</v>
@@ -610,13 +610,13 @@
         <v>2.2893</v>
       </c>
       <c r="S2" t="n">
-        <v>1.3713</v>
+        <v>0.6888</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9687</v>
+        <v>0.433</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4026</v>
+        <v>0.2558</v>
       </c>
       <c r="V2" t="n">
         <v>-1.0543</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P. TREVIÑO QUINTILLÁ</t>
+          <t>O. SIMA FATTY</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8064</v>
+        <v>2.1171</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8801</v>
+        <v>0.2112</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9264</v>
+        <v>1.9059</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.0528</v>
+        <v>-1.5289</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.6079</v>
+        <v>-0.8741</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5552</v>
+        <v>-0.6548</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.2932</v>
+        <v>-1.9124</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.0198</v>
+        <v>-0.0044</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7266</v>
+        <v>-1.908</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.7595</v>
+        <v>0.3835</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.5881</v>
+        <v>-0.8697</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.1714</v>
+        <v>1.2532</v>
       </c>
       <c r="P3" t="n">
         <v>1.6649</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.7055</v>
+        <v>1.6649</v>
       </c>
       <c r="S3" t="n">
-        <v>1.4242</v>
+        <v>-0.1311</v>
       </c>
       <c r="T3" t="n">
-        <v>1.0464</v>
+        <v>-0.2114</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3778</v>
+        <v>0.0803</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.23</v>
+        <v>2.1122</v>
       </c>
       <c r="W3" t="n">
-        <v>1.1675</v>
+        <v>2.3351</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.3975</v>
+        <v>-0.2229</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R. HAYES</t>
+          <t>S. ROMERO SANCHEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6478</v>
+        <v>1.7667</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.08740000000000001</v>
+        <v>-0.1352</v>
       </c>
       <c r="F4" t="n">
-        <v>1.7352</v>
+        <v>1.9019</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7223000000000001</v>
+        <v>2.5177</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.0771</v>
+        <v>-0.4924</v>
       </c>
       <c r="I4" t="n">
-        <v>1.7994</v>
+        <v>3.0102</v>
       </c>
       <c r="J4" t="n">
-        <v>0.649</v>
+        <v>2.1465</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.2523</v>
+        <v>0.2834</v>
       </c>
       <c r="L4" t="n">
-        <v>0.9013</v>
+        <v>1.8631</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0733</v>
+        <v>0.3713</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.8248</v>
+        <v>-0.7758</v>
       </c>
       <c r="O4" t="n">
-        <v>0.8981</v>
+        <v>1.1471</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.2487</v>
+        <v>-0.2081</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.1218</v>
+        <v>-2.0812</v>
       </c>
       <c r="R4" t="n">
         <v>1.8731</v>
       </c>
       <c r="S4" t="n">
-        <v>2.1849</v>
+        <v>-0.6562</v>
       </c>
       <c r="T4" t="n">
-        <v>1.6955</v>
+        <v>-0.4305</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4894</v>
+        <v>-0.2257</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.0106</v>
+        <v>0.1132</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6899</v>
+        <v>0.23</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.7005</v>
+        <v>-0.1168</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>O. SIMA FATTY</t>
+          <t>P. TREVIÑO QUINTILLÁ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6461</v>
+        <v>1.2543</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.3479</v>
+        <v>0.4748</v>
       </c>
       <c r="F5" t="n">
-        <v>1.994</v>
+        <v>0.7796</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.5289</v>
+        <v>-1.0528</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.8741</v>
+        <v>-1.6079</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.6548</v>
+        <v>0.5552</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.9124</v>
+        <v>-0.2932</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.0044</v>
+        <v>-1.0198</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.908</v>
+        <v>0.7266</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3835</v>
+        <v>-0.7595</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.8697</v>
+        <v>-0.5881</v>
       </c>
       <c r="O5" t="n">
-        <v>1.2532</v>
+        <v>-0.1714</v>
       </c>
       <c r="P5" t="n">
         <v>1.6649</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R5" t="n">
-        <v>1.6649</v>
+        <v>2.7055</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.6021</v>
+        <v>0.8721</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7705</v>
+        <v>0.6411</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1684</v>
+        <v>0.231</v>
       </c>
       <c r="V5" t="n">
-        <v>2.1122</v>
+        <v>-0.23</v>
       </c>
       <c r="W5" t="n">
-        <v>2.3351</v>
+        <v>1.1675</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2229</v>
+        <v>-1.3975</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. ROMERO SANCHEZ</t>
+          <t>D. EFAMBE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7775</v>
+        <v>0.4461</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.8015</v>
+        <v>-0.2726</v>
       </c>
       <c r="F6" t="n">
-        <v>1.579</v>
+        <v>0.7187</v>
       </c>
       <c r="G6" t="n">
-        <v>2.5177</v>
+        <v>-1.4022</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4924</v>
+        <v>-0.2494</v>
       </c>
       <c r="I6" t="n">
-        <v>3.0102</v>
+        <v>-1.1528</v>
       </c>
       <c r="J6" t="n">
-        <v>2.1465</v>
+        <v>0.2307</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2834</v>
+        <v>-0.0044</v>
       </c>
       <c r="L6" t="n">
-        <v>1.8631</v>
+        <v>0.2351</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3713</v>
+        <v>-1.6329</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.7758</v>
+        <v>-0.245</v>
       </c>
       <c r="O6" t="n">
-        <v>1.1471</v>
+        <v>-1.3879</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.2081</v>
+        <v>0.4162</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.0812</v>
+        <v>-1.0406</v>
       </c>
       <c r="R6" t="n">
-        <v>1.8731</v>
+        <v>1.4568</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.6454</v>
+        <v>0.7245</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.0967</v>
+        <v>0.5372</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5486</v>
+        <v>0.1873</v>
       </c>
       <c r="V6" t="n">
-        <v>0.1132</v>
+        <v>0.7076</v>
       </c>
       <c r="W6" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1168</v>
+        <v>0.7076</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. EFAMBE</t>
+          <t>R. HAYES</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1437</v>
+        <v>-0.1813</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.487</v>
+        <v>-1.5642</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6307</v>
+        <v>1.3829</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.4022</v>
+        <v>0.7223000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2494</v>
+        <v>-1.0771</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.1528</v>
+        <v>1.7994</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2307</v>
+        <v>0.649</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.0044</v>
+        <v>-0.2523</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2351</v>
+        <v>0.9013</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.6329</v>
+        <v>0.0733</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.245</v>
+        <v>-0.8248</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.3879</v>
+        <v>0.8981</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4162</v>
+        <v>-1.2487</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.0406</v>
+        <v>-3.1218</v>
       </c>
       <c r="R7" t="n">
-        <v>1.4568</v>
+        <v>1.8731</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4221</v>
+        <v>0.3557</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3229</v>
+        <v>0.2187</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0992</v>
+        <v>0.1371</v>
       </c>
       <c r="V7" t="n">
-        <v>0.7076</v>
+        <v>-0.0106</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.6899</v>
       </c>
       <c r="X7" t="n">
-        <v>0.7076</v>
+        <v>-0.7005</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5587</v>
+        <v>-0.3107</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8905</v>
+        <v>-0.76</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3319</v>
+        <v>0.4493</v>
       </c>
       <c r="G8" t="n">
         <v>3.3599</v>
@@ -1078,13 +1078,13 @@
         <v>2.0812</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5461</v>
+        <v>-0.2981</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5129</v>
+        <v>-0.3824</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0332</v>
+        <v>0.0842</v>
       </c>
       <c r="V8" t="n">
         <v>-1.2914</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.1831</v>
+        <v>-1.2862</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2879</v>
+        <v>0.4622</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.8952</v>
+        <v>-1.7484</v>
       </c>
       <c r="G9" t="n">
         <v>-0.9053</v>
@@ -1156,13 +1156,13 @@
         <v>1.4568</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5265</v>
+        <v>0.3704</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5219</v>
+        <v>0.2281</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0045</v>
+        <v>0.1423</v>
       </c>
       <c r="V9" t="n">
         <v>-1.1675</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.0447</v>
+        <v>-3.2358</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.6423</v>
+        <v>-2.8922</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.4023</v>
+        <v>-0.3436</v>
       </c>
       <c r="G10" t="n">
         <v>-0.3948</v>
@@ -1234,13 +1234,13 @@
         <v>1.2487</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3895</v>
+        <v>0.4193</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3262</v>
+        <v>0.4239</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0633</v>
+        <v>-0.0045</v>
       </c>
       <c r="V10" t="n">
         <v>-0.3467</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>7.4655</v>
+        <v>8.1181</v>
       </c>
       <c r="E11" t="n">
-        <v>2.7153</v>
+        <v>3.367900000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>4.7505</v>
+        <v>4.750299999999999</v>
       </c>
       <c r="G11" t="n">
         <v>9.0213</v>
@@ -1294,10 +1294,10 @@
         <v>13.8586</v>
       </c>
       <c r="M11" t="n">
-        <v>-7.798400000000001</v>
+        <v>-7.7984</v>
       </c>
       <c r="N11" t="n">
-        <v>-5.3492</v>
+        <v>-5.349200000000001</v>
       </c>
       <c r="O11" t="n">
         <v>-2.449</v>
@@ -1312,19 +1312,19 @@
         <v>16.6494</v>
       </c>
       <c r="S11" t="n">
-        <v>1.692899999999999</v>
+        <v>2.3454</v>
       </c>
       <c r="T11" t="n">
-        <v>0.8052999999999999</v>
+        <v>1.4577</v>
       </c>
       <c r="U11" t="n">
-        <v>0.8877999999999999</v>
+        <v>0.8878000000000001</v>
       </c>
       <c r="V11" t="n">
         <v>-1.1675</v>
       </c>
       <c r="W11" t="n">
-        <v>3.821000000000001</v>
+        <v>3.821</v>
       </c>
       <c r="X11" t="n">
         <v>-4.9885</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>H. ARBOSA ROLDAN</t>
+          <t>M. DE PABLO DEL CASTILLO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4.406</v>
+        <v>4.0541</v>
       </c>
       <c r="E12" t="n">
-        <v>4.2674</v>
+        <v>6.3132</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1387</v>
+        <v>-2.2591</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5743</v>
+        <v>2.244</v>
       </c>
       <c r="H12" t="n">
-        <v>1.4111</v>
+        <v>1.6121</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.8368</v>
+        <v>0.6319</v>
       </c>
       <c r="J12" t="n">
-        <v>3.5872</v>
+        <v>5.118</v>
       </c>
       <c r="K12" t="n">
-        <v>2.8606</v>
+        <v>2.245</v>
       </c>
       <c r="L12" t="n">
-        <v>0.7266</v>
+        <v>2.873</v>
       </c>
       <c r="M12" t="n">
-        <v>-3.0129</v>
+        <v>-2.874</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.4495</v>
+        <v>-0.6329</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.5634</v>
+        <v>-2.2411</v>
       </c>
       <c r="P12" t="n">
-        <v>2.7055</v>
+        <v>2.2893</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2.7055</v>
+        <v>2.2893</v>
       </c>
       <c r="S12" t="n">
-        <v>0.7724</v>
+        <v>-0.4792</v>
       </c>
       <c r="T12" t="n">
-        <v>1.034</v>
+        <v>0.0277</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2616</v>
+        <v>-0.5069</v>
       </c>
       <c r="V12" t="n">
-        <v>0.3538</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.3538</v>
+        <v>1.1675</v>
       </c>
       <c r="X12" t="n">
-        <v>0.7076</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>M. DE PABLO DEL CASTILLO</t>
+          <t>H. ARBOSA ROLDAN</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.4581</v>
+        <v>3.8409</v>
       </c>
       <c r="E13" t="n">
-        <v>6.0989</v>
+        <v>3.7316</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.6408</v>
+        <v>0.1093</v>
       </c>
       <c r="G13" t="n">
-        <v>2.244</v>
+        <v>0.5743</v>
       </c>
       <c r="H13" t="n">
-        <v>1.6121</v>
+        <v>1.4111</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6319</v>
+        <v>-0.8368</v>
       </c>
       <c r="J13" t="n">
-        <v>5.118</v>
+        <v>3.5872</v>
       </c>
       <c r="K13" t="n">
-        <v>2.245</v>
+        <v>2.8606</v>
       </c>
       <c r="L13" t="n">
-        <v>2.873</v>
+        <v>0.7266</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.874</v>
+        <v>-3.0129</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.6329</v>
+        <v>-1.4495</v>
       </c>
       <c r="O13" t="n">
-        <v>-2.2411</v>
+        <v>-1.5634</v>
       </c>
       <c r="P13" t="n">
-        <v>2.2893</v>
+        <v>2.7055</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.2893</v>
+        <v>2.7055</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.0752</v>
+        <v>0.2073</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1866</v>
+        <v>0.4982</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.8885</v>
+        <v>-0.2909</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.3538</v>
       </c>
       <c r="W13" t="n">
-        <v>1.1675</v>
+        <v>-0.3538</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.1675</v>
+        <v>0.7076</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.6917</v>
+        <v>2.2045</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.0936</v>
+        <v>-0.665</v>
       </c>
       <c r="F14" t="n">
-        <v>2.7854</v>
+        <v>2.8695</v>
       </c>
       <c r="G14" t="n">
         <v>0.5373</v>
@@ -1546,13 +1546,13 @@
         <v>2.0812</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.4802</v>
+        <v>0.0326</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8358</v>
+        <v>-0.4071</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3556</v>
+        <v>0.4398</v>
       </c>
       <c r="V14" t="n">
         <v>1.6345</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.3129</v>
+        <v>-0.0629</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.2595</v>
+        <v>-0.1524</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.0534</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="G15" t="n">
         <v>-0.1906</v>
@@ -1624,13 +1624,13 @@
         <v>1.8731</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1305</v>
+        <v>0.1195</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3824</v>
+        <v>-0.2752</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2519</v>
+        <v>0.3948</v>
       </c>
       <c r="V15" t="n">
         <v>-0.8244</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. PA MOR</t>
+          <t>C. JACOBS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-2.1452</v>
+        <v>-1.6124</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.2825</v>
+        <v>-0.7372</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1373</v>
+        <v>-0.8752</v>
       </c>
       <c r="G16" t="n">
-        <v>-3.9357</v>
+        <v>-1.3288</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8127</v>
+        <v>-1.7762</v>
       </c>
       <c r="I16" t="n">
-        <v>-4.7483</v>
+        <v>0.4474</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.527</v>
+        <v>0.1858</v>
       </c>
       <c r="K16" t="n">
-        <v>1.017</v>
+        <v>-1.4332</v>
       </c>
       <c r="L16" t="n">
-        <v>-2.544</v>
+        <v>1.6189</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.4086</v>
+        <v>-1.5146</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.2043</v>
+        <v>-0.3431</v>
       </c>
       <c r="O16" t="n">
-        <v>-2.2043</v>
+        <v>-1.1716</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.8325</v>
+        <v>0.6244</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.1218</v>
+        <v>-1.0406</v>
       </c>
       <c r="R16" t="n">
-        <v>2.2893</v>
+        <v>1.6649</v>
       </c>
       <c r="S16" t="n">
-        <v>0.8716</v>
+        <v>0.0225</v>
       </c>
       <c r="T16" t="n">
-        <v>0.9687</v>
+        <v>-0.4662</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.09710000000000001</v>
+        <v>0.4887</v>
       </c>
       <c r="V16" t="n">
-        <v>1.7513</v>
+        <v>-0.9305</v>
       </c>
       <c r="W16" t="n">
-        <v>1.3975</v>
+        <v>0.5838</v>
       </c>
       <c r="X16" t="n">
-        <v>0.3538</v>
+        <v>-1.5142</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C. JACOBS</t>
+          <t>J. PARDINA MOLINA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.3689</v>
+        <v>-2.6273</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.3802</v>
+        <v>-0.3037</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.9887</v>
+        <v>-2.3236</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.3288</v>
+        <v>-0.5574</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.7762</v>
+        <v>-0.746</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4474</v>
+        <v>0.1886</v>
       </c>
       <c r="J17" t="n">
-        <v>0.1858</v>
+        <v>1.9574</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.4332</v>
+        <v>-0.5417</v>
       </c>
       <c r="L17" t="n">
-        <v>1.6189</v>
+        <v>2.4991</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.5146</v>
+        <v>-2.5148</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3431</v>
+        <v>-0.2043</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.1716</v>
+        <v>-2.3105</v>
       </c>
       <c r="P17" t="n">
-        <v>0.6244</v>
+        <v>1.8731</v>
       </c>
       <c r="Q17" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R17" t="n">
-        <v>1.6649</v>
+        <v>2.9137</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.7339</v>
+        <v>-0.7835</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.1091</v>
+        <v>-0.5129</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3752</v>
+        <v>-0.2707</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.9305</v>
+        <v>-3.1594</v>
       </c>
       <c r="W17" t="n">
-        <v>0.5838</v>
+        <v>-0.7076</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.5142</v>
+        <v>-2.4518</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. PARDINA MOLINA</t>
+          <t>E. A NONGO BERTHOLD</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.6821</v>
+        <v>-3.2279</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.3037</v>
+        <v>-3.784</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.3784</v>
+        <v>0.5561</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.5574</v>
+        <v>-0.8148</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.746</v>
+        <v>-0.9275</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1886</v>
+        <v>0.1127</v>
       </c>
       <c r="J18" t="n">
-        <v>1.9574</v>
+        <v>-0.5984</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.5417</v>
+        <v>-0.6375999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>2.4991</v>
+        <v>0.0392</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.5148</v>
+        <v>-0.2164</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2043</v>
+        <v>-0.2899</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.3105</v>
+        <v>0.0735</v>
       </c>
       <c r="P18" t="n">
-        <v>1.8731</v>
+        <v>-2.4974</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.0406</v>
+        <v>-3.1218</v>
       </c>
       <c r="R18" t="n">
-        <v>2.9137</v>
+        <v>0.6244</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8383</v>
+        <v>0.2011</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5129</v>
+        <v>-0.0638</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3255</v>
+        <v>0.2649</v>
       </c>
       <c r="V18" t="n">
-        <v>-3.1594</v>
+        <v>-0.1168</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.7076</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.4518</v>
+        <v>-0.1168</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E. A NONGO BERTHOLD</t>
+          <t>D. PA MOR</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.02</v>
+        <v>-3.2373</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.4625</v>
+        <v>-3.1398</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4426</v>
+        <v>-0.0975</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.8148</v>
+        <v>-3.9357</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.9275</v>
+        <v>0.8127</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1127</v>
+        <v>-4.7483</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.5984</v>
+        <v>-1.527</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.6375999999999999</v>
+        <v>1.017</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0392</v>
+        <v>-2.544</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.2164</v>
+        <v>-2.4086</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2899</v>
+        <v>-0.2043</v>
       </c>
       <c r="O19" t="n">
-        <v>0.0735</v>
+        <v>-2.2043</v>
       </c>
       <c r="P19" t="n">
-        <v>-2.4974</v>
+        <v>-0.8325</v>
       </c>
       <c r="Q19" t="n">
         <v>-3.1218</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6244</v>
+        <v>2.2893</v>
       </c>
       <c r="S19" t="n">
-        <v>0.4091</v>
+        <v>-0.2205</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2577</v>
+        <v>0.1115</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1514</v>
+        <v>-0.332</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.1168</v>
+        <v>1.7513</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.3975</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.1168</v>
+        <v>0.3538</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-6.4924</v>
+        <v>-6.0829</v>
       </c>
       <c r="E20" t="n">
-        <v>-6.3345</v>
+        <v>-6.013</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.158</v>
+        <v>-0.0699</v>
       </c>
       <c r="G20" t="n">
         <v>-5.5497</v>
@@ -2014,13 +2014,13 @@
         <v>2.2893</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.488</v>
+        <v>-0.0785</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1214</v>
+        <v>0.2001</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3666</v>
+        <v>-0.2785</v>
       </c>
       <c r="V20" t="n">
         <v>2.4589</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-7.465700000000002</v>
+        <v>-6.751199999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.7502</v>
+        <v>-4.750299999999998</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.7153</v>
+        <v>-2.001</v>
       </c>
       <c r="G21" t="n">
         <v>-9.0214</v>
@@ -2065,10 +2065,10 @@
         <v>-11.4095</v>
       </c>
       <c r="J21" t="n">
-        <v>7.798500000000001</v>
+        <v>7.798500000000002</v>
       </c>
       <c r="K21" t="n">
-        <v>5.3493</v>
+        <v>5.349300000000001</v>
       </c>
       <c r="L21" t="n">
         <v>2.4492</v>
@@ -2092,13 +2092,13 @@
         <v>18.7307</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.693</v>
+        <v>-0.9787</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8877999999999999</v>
+        <v>-0.8877000000000002</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.8051999999999999</v>
+        <v>-0.09080000000000005</v>
       </c>
       <c r="V21" t="n">
         <v>1.1674</v>
